--- a/output/tables/empirical_facts.xlsx
+++ b/output/tables/empirical_facts.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="241" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="491" uniqueCount="52">
   <si>
     <t>risk_group</t>
   </si>
@@ -264,34 +264,34 @@
         <v>0</v>
       </c>
       <c r="B2" s="1">
-        <v>4824</v>
+        <v>4818</v>
       </c>
       <c r="C2" s="1">
-        <v>906332</v>
+        <v>905574</v>
       </c>
       <c r="D2" s="1">
-        <v>256</v>
+        <v>292</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
       </c>
       <c r="F2" s="1">
-        <v>1031167</v>
+        <v>1030411</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
       </c>
       <c r="H2" s="1">
-        <v>0.28245720267295837</v>
+        <v>0.32244741916656494</v>
       </c>
       <c r="I2" s="1">
-        <v>0.034596119076013565</v>
+        <v>0.036978859454393387</v>
       </c>
       <c r="J2" s="1">
-        <v>0.24786108732223511</v>
+        <v>0.28546854853630066</v>
       </c>
       <c r="K2" s="1">
-        <v>0.31705331802368164</v>
+        <v>0.35942628979682922</v>
       </c>
     </row>
     <row r="3">
@@ -299,34 +299,34 @@
         <v>1</v>
       </c>
       <c r="B3" s="1">
-        <v>758</v>
+        <v>747</v>
       </c>
       <c r="C3" s="1">
-        <v>395630</v>
+        <v>391712</v>
       </c>
       <c r="D3" s="1">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="E3" s="1">
-        <v>4992073.4280319214</v>
+        <v>4874047.1994400025</v>
       </c>
       <c r="F3" s="1">
-        <v>532897</v>
+        <v>526967</v>
       </c>
       <c r="G3" s="1">
-        <v>9.3678016662597656</v>
+        <v>9.2492456436157227</v>
       </c>
       <c r="H3" s="1">
-        <v>0.14407400786876678</v>
+        <v>0.16849114000797272</v>
       </c>
       <c r="I3" s="1">
-        <v>0.037400119006633759</v>
+        <v>0.040646631270647049</v>
       </c>
       <c r="J3" s="1">
-        <v>0.10667388886213303</v>
+        <v>0.12784451246261597</v>
       </c>
       <c r="K3" s="1">
-        <v>0.18147411942481995</v>
+        <v>0.20913776755332947</v>
       </c>
     </row>
     <row r="4">
@@ -334,34 +334,34 @@
         <v>2</v>
       </c>
       <c r="B4" s="1">
-        <v>978</v>
+        <v>966</v>
       </c>
       <c r="C4" s="1">
-        <v>396368</v>
+        <v>393006</v>
       </c>
       <c r="D4" s="1">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="E4" s="1">
-        <v>18917342.532976151</v>
+        <v>18600633.659166336</v>
       </c>
       <c r="F4" s="1">
-        <v>497182</v>
+        <v>495034</v>
       </c>
       <c r="G4" s="1">
-        <v>38.049129486083984</v>
+        <v>37.574455261230469</v>
       </c>
       <c r="H4" s="1">
-        <v>0.28508859872817993</v>
+        <v>0.30788335204124451</v>
       </c>
       <c r="I4" s="1">
-        <v>0.052557513117790222</v>
+        <v>0.05485076829791069</v>
       </c>
       <c r="J4" s="1">
-        <v>0.23253108561038971</v>
+        <v>0.25303259491920471</v>
       </c>
       <c r="K4" s="1">
-        <v>0.33764612674713135</v>
+        <v>0.3627341091632843</v>
       </c>
     </row>
     <row r="5">
@@ -369,34 +369,34 @@
         <v>3</v>
       </c>
       <c r="B5" s="1">
-        <v>1108</v>
+        <v>1089</v>
       </c>
       <c r="C5" s="1">
-        <v>395563</v>
+        <v>392128</v>
       </c>
       <c r="D5" s="1">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="E5" s="1">
-        <v>44143857.528526306</v>
+        <v>43148675.044975281</v>
       </c>
       <c r="F5" s="1">
-        <v>481656</v>
+        <v>477588</v>
       </c>
       <c r="G5" s="1">
-        <v>91.650177001953125</v>
+        <v>90.347068786621094</v>
       </c>
       <c r="H5" s="1">
-        <v>0.39943069219589233</v>
+        <v>0.43098172545433044</v>
       </c>
       <c r="I5" s="1">
-        <v>0.062270477414131165</v>
+        <v>0.06496477872133255</v>
       </c>
       <c r="J5" s="1">
-        <v>0.33716022968292236</v>
+        <v>0.36601695418357849</v>
       </c>
       <c r="K5" s="1">
-        <v>0.46170115470886231</v>
+        <v>0.4959464967250824</v>
       </c>
     </row>
     <row r="6">
@@ -404,34 +404,34 @@
         <v>4</v>
       </c>
       <c r="B6" s="1">
-        <v>1250</v>
+        <v>1244</v>
       </c>
       <c r="C6" s="1">
-        <v>395607</v>
+        <v>392541</v>
       </c>
       <c r="D6" s="1">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="E6" s="1">
-        <v>100141460.08504295</v>
+        <v>97506488.08571434</v>
       </c>
       <c r="F6" s="1">
-        <v>471867</v>
+        <v>468662</v>
       </c>
       <c r="G6" s="1">
-        <v>212.22390747070313</v>
+        <v>208.05290222167969</v>
       </c>
       <c r="H6" s="1">
-        <v>0.63699579238891602</v>
+        <v>0.68018370866775513</v>
       </c>
       <c r="I6" s="1">
-        <v>0.07862379401922226</v>
+        <v>0.081560321152210236</v>
       </c>
       <c r="J6" s="1">
-        <v>0.55837202072143555</v>
+        <v>0.59862339496612549</v>
       </c>
       <c r="K6" s="1">
-        <v>0.71561956405639649</v>
+        <v>0.76174402236938477</v>
       </c>
     </row>
     <row r="7">
@@ -439,34 +439,34 @@
         <v>5</v>
       </c>
       <c r="B7" s="1">
-        <v>1208</v>
+        <v>1194</v>
       </c>
       <c r="C7" s="1">
-        <v>396330</v>
+        <v>392271</v>
       </c>
       <c r="D7" s="1">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="E7" s="1">
-        <v>208466282.7444191</v>
+        <v>201871359.55514908</v>
       </c>
       <c r="F7" s="1">
-        <v>457669</v>
+        <v>452414</v>
       </c>
       <c r="G7" s="1">
-        <v>455.49575805664063</v>
+        <v>446.2093505859375</v>
       </c>
       <c r="H7" s="1">
-        <v>0.56266242265701294</v>
+        <v>0.61692047119140625</v>
       </c>
       <c r="I7" s="1">
-        <v>0.073829397559165955</v>
+        <v>0.07770402729511261</v>
       </c>
       <c r="J7" s="1">
-        <v>0.48883301019668579</v>
+        <v>0.53921645879745483</v>
       </c>
       <c r="K7" s="1">
-        <v>0.63649183511734009</v>
+        <v>0.69462448358535767</v>
       </c>
     </row>
     <row r="8">
@@ -474,34 +474,34 @@
         <v>6</v>
       </c>
       <c r="B8" s="1">
-        <v>1256</v>
+        <v>1252</v>
       </c>
       <c r="C8" s="1">
-        <v>395992</v>
+        <v>391998</v>
       </c>
       <c r="D8" s="1">
-        <v>222</v>
+        <v>250</v>
       </c>
       <c r="E8" s="1">
-        <v>403585574.56385613</v>
+        <v>391804841.68510246</v>
       </c>
       <c r="F8" s="1">
-        <v>443613</v>
+        <v>440367</v>
       </c>
       <c r="G8" s="1">
-        <v>909.76947021484375</v>
+        <v>889.72344970703125</v>
       </c>
       <c r="H8" s="1">
-        <v>0.56061738729476929</v>
+        <v>0.63775837421417236</v>
       </c>
       <c r="I8" s="1">
-        <v>0.073726631700992584</v>
+        <v>0.079032130539417267</v>
       </c>
       <c r="J8" s="1">
-        <v>0.4868907630443573</v>
+        <v>0.55872625112533569</v>
       </c>
       <c r="K8" s="1">
-        <v>0.63434404134750366</v>
+        <v>0.71679049730300903</v>
       </c>
     </row>
     <row r="9">
@@ -509,34 +509,34 @@
         <v>7</v>
       </c>
       <c r="B9" s="1">
-        <v>1383</v>
+        <v>1363</v>
       </c>
       <c r="C9" s="1">
-        <v>395996</v>
+        <v>392460</v>
       </c>
       <c r="D9" s="1">
-        <v>266</v>
+        <v>285</v>
       </c>
       <c r="E9" s="1">
-        <v>845328304.84852266</v>
+        <v>817340071.53259707</v>
       </c>
       <c r="F9" s="1">
-        <v>444043</v>
+        <v>439584</v>
       </c>
       <c r="G9" s="1">
-        <v>1903.708251953125</v>
+        <v>1859.3489990234375</v>
       </c>
       <c r="H9" s="1">
-        <v>0.67172396183013916</v>
+        <v>0.72618865966796875</v>
       </c>
       <c r="I9" s="1">
-        <v>0.080697521567344666</v>
+        <v>0.084280163049697876</v>
       </c>
       <c r="J9" s="1">
-        <v>0.5910264253616333</v>
+        <v>0.64190852642059326</v>
       </c>
       <c r="K9" s="1">
-        <v>0.75242149829864502</v>
+        <v>0.81046879291534424</v>
       </c>
     </row>
     <row r="10">
@@ -544,34 +544,34 @@
         <v>8</v>
       </c>
       <c r="B10" s="1">
-        <v>1314</v>
+        <v>1284</v>
       </c>
       <c r="C10" s="1">
-        <v>395910</v>
+        <v>392429</v>
       </c>
       <c r="D10" s="1">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E10" s="1">
-        <v>1855467196.3244739</v>
+        <v>1819628455.9792786</v>
       </c>
       <c r="F10" s="1">
-        <v>443662</v>
+        <v>442462</v>
       </c>
       <c r="G10" s="1">
-        <v>4182.1640625</v>
+        <v>4112.5078125</v>
       </c>
       <c r="H10" s="1">
-        <v>0.52789777517318726</v>
+        <v>0.54277336597442627</v>
       </c>
       <c r="I10" s="1">
-        <v>0.071551389992237091</v>
+        <v>0.072873041033744812</v>
       </c>
       <c r="J10" s="1">
-        <v>0.45634639263153076</v>
+        <v>0.46990031003952026</v>
       </c>
       <c r="K10" s="1">
-        <v>0.59944915771484375</v>
+        <v>0.61564642190933228</v>
       </c>
     </row>
     <row r="11">
@@ -579,34 +579,34 @@
         <v>9</v>
       </c>
       <c r="B11" s="1">
-        <v>1215</v>
+        <v>1190</v>
       </c>
       <c r="C11" s="1">
-        <v>395775</v>
+        <v>392093</v>
       </c>
       <c r="D11" s="1">
-        <v>388</v>
+        <v>432</v>
       </c>
       <c r="E11" s="1">
-        <v>4411237953.5526857</v>
+        <v>4349091802.7986784</v>
       </c>
       <c r="F11" s="1">
-        <v>444974</v>
+        <v>441899</v>
       </c>
       <c r="G11" s="1">
-        <v>9913.4736328125</v>
+        <v>9841.8232421875</v>
       </c>
       <c r="H11" s="1">
-        <v>0.98035502433776856</v>
+        <v>1.1017794609069824</v>
       </c>
       <c r="I11" s="1">
-        <v>0.097501344978809357</v>
+        <v>0.1038411483168602</v>
       </c>
       <c r="J11" s="1">
-        <v>0.8828536868095398</v>
+        <v>0.99793833494186401</v>
       </c>
       <c r="K11" s="1">
-        <v>1.0778564214706421</v>
+        <v>1.2056206464767456</v>
       </c>
     </row>
     <row r="12">
@@ -614,34 +614,34 @@
         <v>10</v>
       </c>
       <c r="B12" s="1">
-        <v>1023</v>
+        <v>996</v>
       </c>
       <c r="C12" s="1">
-        <v>395884</v>
+        <v>392489</v>
       </c>
       <c r="D12" s="1">
-        <v>1332</v>
+        <v>1432</v>
       </c>
       <c r="E12" s="1">
-        <v>15192259085.434868</v>
+        <v>15093254311.424252</v>
       </c>
       <c r="F12" s="1">
-        <v>447574</v>
+        <v>444194</v>
       </c>
       <c r="G12" s="1">
-        <v>33943.5703125</v>
+        <v>33978.96875</v>
       </c>
       <c r="H12" s="1">
-        <v>3.3646218776702881</v>
+        <v>3.6485099792480469</v>
       </c>
       <c r="I12" s="1">
-        <v>0.18038830161094666</v>
+        <v>0.18862809240818024</v>
       </c>
       <c r="J12" s="1">
-        <v>3.1842336654663086</v>
+        <v>3.4598817825317383</v>
       </c>
       <c r="K12" s="1">
-        <v>3.5450100898742676</v>
+        <v>3.8371381759643555</v>
       </c>
     </row>
   </sheetData>
@@ -675,16 +675,16 @@
         <v>12</v>
       </c>
       <c r="B2" s="1">
-        <v>5146355</v>
+        <v>5099026</v>
       </c>
       <c r="C2" s="1">
-        <v>3694</v>
+        <v>4007</v>
       </c>
       <c r="D2" s="1">
-        <v>0.71778959035873413</v>
+        <v>0.78583633899688721</v>
       </c>
       <c r="E2" s="1">
-        <v>0.02313922718167305</v>
+        <v>0.024322478100657463</v>
       </c>
     </row>
     <row r="3">
@@ -692,16 +692,16 @@
         <v>13</v>
       </c>
       <c r="B3" s="1">
-        <v>2963208</v>
+        <v>2952627</v>
       </c>
       <c r="C3" s="1">
-        <v>958</v>
+        <v>1090</v>
       </c>
       <c r="D3" s="1">
-        <v>0.32329827547073364</v>
+        <v>0.36916276812553406</v>
       </c>
       <c r="E3" s="1">
-        <v>0.020469464361667633</v>
+        <v>0.021911926567554474</v>
       </c>
     </row>
     <row r="4">
@@ -709,16 +709,16 @@
         <v>14</v>
       </c>
       <c r="B4" s="1">
-        <v>2182894</v>
+        <v>2146146</v>
       </c>
       <c r="C4" s="1">
-        <v>2736</v>
+        <v>2917</v>
       </c>
       <c r="D4" s="1">
-        <v>1.2533819675445557</v>
+        <v>1.3591805696487427</v>
       </c>
       <c r="E4" s="1">
-        <v>0.046936329454183578</v>
+        <v>0.049291234463453293</v>
       </c>
     </row>
     <row r="5">
@@ -726,16 +726,16 @@
         <v>15</v>
       </c>
       <c r="B5" s="1">
-        <v>4955306</v>
+        <v>4914855</v>
       </c>
       <c r="C5" s="1">
-        <v>3087</v>
+        <v>3359</v>
       </c>
       <c r="D5" s="1">
-        <v>0.62296861410140991</v>
+        <v>0.68343824148178101</v>
       </c>
       <c r="E5" s="1">
-        <v>0.021969420835375786</v>
+        <v>0.023104783147573471</v>
       </c>
     </row>
     <row r="6">
@@ -743,16 +743,16 @@
         <v>16</v>
       </c>
       <c r="B6" s="1">
-        <v>191049</v>
+        <v>184171</v>
       </c>
       <c r="C6" s="1">
-        <v>607</v>
+        <v>648</v>
       </c>
       <c r="D6" s="1">
-        <v>3.1771953105926514</v>
+        <v>3.5184693336486816</v>
       </c>
       <c r="E6" s="1">
-        <v>0.25235658884048462</v>
+        <v>0.27043130993843079</v>
       </c>
     </row>
     <row r="7">
@@ -760,16 +760,16 @@
         <v>17</v>
       </c>
       <c r="B7" s="1">
-        <v>116945</v>
+        <v>114887</v>
       </c>
       <c r="C7" s="1">
-        <v>435</v>
+        <v>464</v>
       </c>
       <c r="D7" s="1">
-        <v>3.7196972370147705</v>
+        <v>4.0387511253356934</v>
       </c>
       <c r="E7" s="1">
-        <v>0.34890711307525635</v>
+        <v>0.36674600839614868</v>
       </c>
     </row>
     <row r="8">
@@ -777,16 +777,16 @@
         <v>18</v>
       </c>
       <c r="B8" s="1">
-        <v>79774</v>
+        <v>79017</v>
       </c>
       <c r="C8" s="1">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="D8" s="1">
-        <v>4.3372526168823242</v>
+        <v>4.6572256088256836</v>
       </c>
       <c r="E8" s="1">
-        <v>0.45602524280548096</v>
+        <v>0.4747290313243866</v>
       </c>
     </row>
     <row r="9">
@@ -794,16 +794,16 @@
         <v>19</v>
       </c>
       <c r="B9" s="1">
-        <v>45461</v>
+        <v>42882</v>
       </c>
       <c r="C9" s="1">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="D9" s="1">
-        <v>4.3113880157470703</v>
+        <v>4.8038802146911621</v>
       </c>
       <c r="E9" s="1">
-        <v>0.60229170322418213</v>
+        <v>0.65443873405456543</v>
       </c>
     </row>
     <row r="10">
@@ -811,16 +811,16 @@
         <v>20</v>
       </c>
       <c r="B10" s="1">
-        <v>8183</v>
+        <v>7501</v>
       </c>
       <c r="C10" s="1">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D10" s="1">
-        <v>6.8434557914733887</v>
+        <v>8.2655649185180664</v>
       </c>
       <c r="E10" s="1">
-        <v>1.7862670421600342</v>
+        <v>2.0489456653594971</v>
       </c>
     </row>
   </sheetData>
@@ -848,16 +848,16 @@
     </row>
     <row r="2">
       <c r="A2" s="1">
-        <v>1700</v>
+        <v>1657</v>
       </c>
       <c r="B2" s="1">
-        <v>15027.9609375</v>
+        <v>15445.1220703125</v>
       </c>
       <c r="C2" s="1">
-        <v>101281.8515625</v>
+        <v>106001.9375</v>
       </c>
       <c r="D2" s="1">
-        <v>352071.28125</v>
+        <v>367425.4375</v>
       </c>
     </row>
   </sheetData>
@@ -1082,7 +1082,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1151,23 +1151,6 @@
       </c>
       <c r="E4" s="1">
         <v>5.7291665077209473</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" s="1">
-        <v>44</v>
-      </c>
-      <c r="C5" s="1">
-        <v>44</v>
-      </c>
-      <c r="D5" s="1">
-        <v>0</v>
-      </c>
-      <c r="E5" s="1">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1201,16 +1184,16 @@
         <v>42</v>
       </c>
       <c r="B2" s="1">
-        <v>1257</v>
+        <v>1214</v>
       </c>
       <c r="C2" s="1">
-        <v>9842.9195388958215</v>
+        <v>10059.369099031861</v>
       </c>
       <c r="D2" s="1">
-        <v>36949.851505571802</v>
+        <v>38786.868824420715</v>
       </c>
       <c r="E2" s="1">
-        <v>169209.13604766634</v>
+        <v>177583.49305253444</v>
       </c>
     </row>
     <row r="3">
@@ -1218,16 +1201,16 @@
         <v>43</v>
       </c>
       <c r="B3" s="1">
-        <v>1574</v>
+        <v>1420</v>
       </c>
       <c r="C3" s="1">
-        <v>156629.140625</v>
+        <v>159264.6875</v>
       </c>
       <c r="D3" s="1">
-        <v>192626.25</v>
+        <v>193959.421875</v>
       </c>
       <c r="E3" s="1">
-        <v>255163.96875</v>
+        <v>254508.96875</v>
       </c>
     </row>
   </sheetData>
@@ -1264,19 +1247,19 @@
         <v>0</v>
       </c>
       <c r="B2" s="1">
-        <v>2963208</v>
+        <v>2952627</v>
       </c>
       <c r="C2" s="1">
-        <v>958</v>
+        <v>1090</v>
       </c>
       <c r="D2" s="1">
-        <v>0.32329827547073364</v>
+        <v>0.36916276812553406</v>
       </c>
       <c r="E2" s="1">
-        <v>0.032329827547073364</v>
+        <v>0.036916278302669525</v>
       </c>
       <c r="F2" s="1">
-        <v>0.020469464361667633</v>
+        <v>0.021911926567554474</v>
       </c>
     </row>
     <row r="3">
@@ -1284,19 +1267,19 @@
         <v>1</v>
       </c>
       <c r="B3" s="1">
-        <v>2182894</v>
+        <v>2146146</v>
       </c>
       <c r="C3" s="1">
-        <v>2736</v>
+        <v>2917</v>
       </c>
       <c r="D3" s="1">
-        <v>1.2533819675445557</v>
+        <v>1.3591805696487427</v>
       </c>
       <c r="E3" s="1">
-        <v>0.12533819675445557</v>
+        <v>0.13591806590557098</v>
       </c>
       <c r="F3" s="1">
-        <v>0.046936329454183578</v>
+        <v>0.049291234463453293</v>
       </c>
     </row>
   </sheetData>
@@ -1324,13 +1307,13 @@
     </row>
     <row r="2">
       <c r="A2" s="1">
-        <v>0.017162783071398735</v>
+        <v>0.017442354932427406</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
       </c>
       <c r="C2" s="1">
-        <v>5146102</v>
+        <v>5098773</v>
       </c>
       <c r="D2" t="s">
         <v>51</v>
